--- a/MS_Excel_Practical_Exam_Medium_Level.xlsx
+++ b/MS_Excel_Practical_Exam_Medium_Level.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASDC23\Desktop\Harshi DA-18\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Library5\Downloads\DA 18 Harshi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C6B7BF-BB8A-424C-AC95-49A945F84282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F65C4C3D-91BA-4DCD-AFE1-7BFA536EE681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="88">
   <si>
     <t>Total Questions: 30</t>
   </si>
@@ -280,6 +280,27 @@
   </si>
   <si>
     <t>west</t>
+  </si>
+  <si>
+    <t>A7 High &amp; Low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A8 MAX </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A8 MIN </t>
+  </si>
+  <si>
+    <t>A9 Month Name</t>
+  </si>
+  <si>
+    <t>A12 AVG</t>
+  </si>
+  <si>
+    <t>A13 Avg Max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A14 </t>
   </si>
 </sst>
 </file>
@@ -289,7 +310,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -312,6 +333,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFF0F6FC"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -327,7 +354,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -526,12 +553,51 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
@@ -539,12 +605,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="43" fontId="0" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -552,9 +612,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -566,13 +623,37 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1136,128 +1217,178 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="26" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="G1" s="28" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="20">
         <v>78</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="20">
         <v>82</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="20">
         <v>85</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="20">
         <v>92</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="G2" s="29">
+        <f>AVERAGE(C2:E2)</f>
+        <v>81.666666666666671</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="20">
         <v>88</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="20">
         <v>91</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="20">
         <v>90</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="20">
         <v>96</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="G3" s="29">
+        <f t="shared" ref="G3:G6" si="0">AVERAGE(C3:E3)</f>
+        <v>89.666666666666671</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="20">
         <v>65</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="20">
         <v>70</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="20">
         <v>72</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="20">
         <v>85</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="G4" s="29">
+        <f t="shared" si="0"/>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="20">
         <v>92</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="20">
         <v>89</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="20">
         <v>94</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="20">
         <v>98</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6">
+      <c r="G5" s="29">
+        <f t="shared" si="0"/>
+        <v>91.666666666666671</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="27">
         <v>55</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="27">
         <v>60</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="27">
         <v>58</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="27">
         <v>80</v>
       </c>
+      <c r="G6" s="30">
+        <f t="shared" si="0"/>
+        <v>57.666666666666664</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="31" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="32">
+        <f>MAX(G2:G6)</f>
+        <v>91.666666666666671</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="33"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1522,17 +1653,24 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{977BCA3A-0CB3-4E6D-A410-745F4E22A8DA}">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.28515625" style="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14" style="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.28515625" style="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -1554,270 +1692,325 @@
       <c r="G1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="7" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="14">
+      <c r="K1" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="L1" s="19" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="11">
         <v>301</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="15">
-        <v>2</v>
-      </c>
-      <c r="F2" s="15">
+      <c r="E2" s="12">
+        <v>2</v>
+      </c>
+      <c r="F2" s="12">
         <v>45000</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="11">
+      <c r="H2" s="9">
         <f>E2*F2</f>
         <v>90000</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="9">
         <f>H2*VLOOKUP(D2,Product_Master!A2:C4,3,0)%</f>
         <v>16200</v>
       </c>
-      <c r="J2" s="12">
+      <c r="J2" s="9">
         <f>H2+I2</f>
         <v>106200</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="14">
+      <c r="K2" s="4" t="str">
+        <f>IF(E2&gt;3,"High","Low")</f>
+        <v>Low</v>
+      </c>
+      <c r="L2" t="str">
+        <f>TEXT(G2,"MMMM")</f>
+        <v>January</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="11">
+        <v>306</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="12">
+        <v>2</v>
+      </c>
+      <c r="F3" s="12">
+        <v>45000</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="9">
+        <f>E3*F3</f>
+        <v>90000</v>
+      </c>
+      <c r="I3" s="9">
+        <f>H3*VLOOKUP(D3,Product_Master!A1:C4,3,0)%</f>
+        <v>16200</v>
+      </c>
+      <c r="J3" s="9">
+        <f>H3+I3</f>
+        <v>106200</v>
+      </c>
+      <c r="K3" s="4" t="str">
+        <f t="shared" ref="K3:K7" si="0">IF(E3&gt;3,"High","Low")</f>
+        <v>Low</v>
+      </c>
+      <c r="L3" t="str">
+        <f t="shared" ref="L3:L7" si="1">TEXT(G3,"MMMM")</f>
+        <v>January</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="11">
         <v>302</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B4" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C4" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D4" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="15">
+      <c r="E4" s="12">
         <v>5</v>
       </c>
-      <c r="F3" s="15">
+      <c r="F4" s="12">
         <v>15000</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="G4" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="11">
-        <f t="shared" ref="H3:H7" si="0">E3*F3</f>
+      <c r="H4" s="9">
+        <f>E4*F4</f>
         <v>75000</v>
       </c>
-      <c r="I3" s="11">
-        <f>H3*VLOOKUP(D3,Product_Master!A3:C5,3,0)%</f>
+      <c r="I4" s="9">
+        <f>H4*VLOOKUP(D4,Product_Master!A3:C5,3,0)%</f>
         <v>9000</v>
       </c>
-      <c r="J3" s="12">
-        <f t="shared" ref="J3:J7" si="1">H3+I3</f>
+      <c r="J4" s="9">
+        <f>H4+I4</f>
         <v>84000</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="14">
+      <c r="K4" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>High</v>
+      </c>
+      <c r="L4" t="str">
+        <f t="shared" si="1"/>
+        <v>January</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="11">
+        <v>305</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="12">
+        <v>4</v>
+      </c>
+      <c r="F5" s="12">
+        <v>15000</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="9">
+        <f>E5*F5</f>
+        <v>60000</v>
+      </c>
+      <c r="I5" s="9">
+        <f>H5*VLOOKUP(D5,Product_Master!A2:C5,3,0)%</f>
+        <v>7200</v>
+      </c>
+      <c r="J5" s="9">
+        <f>H5+I5</f>
+        <v>67200</v>
+      </c>
+      <c r="K5" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>High</v>
+      </c>
+      <c r="L5" t="str">
+        <f t="shared" si="1"/>
+        <v>January</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="11">
         <v>303</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B6" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C6" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D6" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="15">
+      <c r="E6" s="12">
         <v>3</v>
       </c>
-      <c r="F4" s="15">
+      <c r="F6" s="12">
         <v>18000</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="G6" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="H4" s="11">
+      <c r="H6" s="9">
+        <f>E6*F6</f>
+        <v>54000</v>
+      </c>
+      <c r="I6" s="9">
+        <f>H6*VLOOKUP(D6,Product_Master!A4:C6,3,0)%</f>
+        <v>6480</v>
+      </c>
+      <c r="J6" s="9">
+        <f>H6+I6</f>
+        <v>60480</v>
+      </c>
+      <c r="K6" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>54000</v>
-      </c>
-      <c r="I4" s="11">
-        <f>H4*VLOOKUP(D4,Product_Master!A4:C6,3,0)%</f>
-        <v>6480</v>
-      </c>
-      <c r="J4" s="12">
+        <v>Low</v>
+      </c>
+      <c r="L6" t="str">
         <f t="shared" si="1"/>
-        <v>60480</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="14">
+        <v>January</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="11">
         <v>304</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B7" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C7" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D7" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E7" s="12">
         <v>1</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F7" s="12">
         <v>45000</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G7" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H7" s="9">
+        <f>E7*F7</f>
+        <v>45000</v>
+      </c>
+      <c r="I7" s="9">
+        <f>H7*VLOOKUP(D7,Product_Master!A1:C4,3,0)%</f>
+        <v>8100</v>
+      </c>
+      <c r="J7" s="9">
+        <f>H7+I7</f>
+        <v>53100</v>
+      </c>
+      <c r="K7" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>45000</v>
-      </c>
-      <c r="I5" s="11">
-        <f>H5*VLOOKUP(D5,Product_Master!A1:C4,3,0)%</f>
-        <v>8100</v>
-      </c>
-      <c r="J5" s="12">
+        <v>Low</v>
+      </c>
+      <c r="L7" t="str">
         <f t="shared" si="1"/>
-        <v>53100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="14">
-        <v>305</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="15">
-        <v>4</v>
-      </c>
-      <c r="F6" s="15">
-        <v>15000</v>
-      </c>
-      <c r="G6" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6" s="11">
-        <f t="shared" si="0"/>
-        <v>60000</v>
-      </c>
-      <c r="I6" s="11">
-        <f>H6*VLOOKUP(D6,Product_Master!A2:C5,3,0)%</f>
-        <v>7200</v>
-      </c>
-      <c r="J6" s="12">
-        <f t="shared" si="1"/>
-        <v>67200</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="14">
-        <v>306</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="15">
-        <v>2</v>
-      </c>
-      <c r="F7" s="15">
-        <v>45000</v>
-      </c>
-      <c r="G7" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7" s="11">
-        <f t="shared" si="0"/>
-        <v>90000</v>
-      </c>
-      <c r="I7" s="11">
-        <f>H7*VLOOKUP(D7,Product_Master!A1:C4,3,0)%</f>
-        <v>16200</v>
-      </c>
-      <c r="J7" s="12">
-        <f t="shared" si="1"/>
-        <v>106200</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="7" t="s">
+        <v>January</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="27" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="16">
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="21">
         <f>SUM(J2:J7)</f>
         <v>477180</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17" t="s">
+      <c r="K8" s="6"/>
+    </row>
+    <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="B10" s="18">
+      <c r="B10" s="14">
         <f>COUNTA(E2:E7)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="17" t="s">
+    <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="B12" s="18"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
+      <c r="B12" s="14"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="20">
+      <c r="B13" s="16">
         <f>SUMIF(B2:B7,"North",E2:E7)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>15</v>
       </c>
@@ -1826,7 +2019,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>79</v>
       </c>
@@ -1835,7 +2028,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>80</v>
       </c>
@@ -1844,7 +2037,29 @@
         <v>1</v>
       </c>
     </row>
+    <row r="17" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="24">
+        <f>MAX(Answer!J2:J7)</f>
+        <v>106200</v>
+      </c>
+      <c r="B19" s="25">
+        <f>MIN(J2:J7)</f>
+        <v>53100</v>
+      </c>
+    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J7">
+    <sortCondition descending="1" ref="J2:J7"/>
+  </sortState>
   <mergeCells count="1">
     <mergeCell ref="A8:I8"/>
   </mergeCells>

--- a/MS_Excel_Practical_Exam_Medium_Level.xlsx
+++ b/MS_Excel_Practical_Exam_Medium_Level.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Library5\Downloads\DA 18 Harshi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BAPS\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F65C4C3D-91BA-4DCD-AFE1-7BFA536EE681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C56DC295-79E3-4582-A26B-03AFE9A2E912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,9 @@
     <sheet name="Questions" sheetId="5" r:id="rId5"/>
     <sheet name="Answer" sheetId="6" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Answer!$D$1:$E$8</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -29,15 +32,36 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="96">
   <si>
     <t>Total Questions: 30</t>
   </si>
@@ -300,7 +324,31 @@
     <t>A13 Avg Max</t>
   </si>
   <si>
-    <t xml:space="preserve">A14 </t>
+    <t>A14 CountIF</t>
+  </si>
+  <si>
+    <t>A15</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>A20 Median</t>
+  </si>
+  <si>
+    <t>A21</t>
+  </si>
+  <si>
+    <t>A22 CONCAT</t>
+  </si>
+  <si>
+    <t>A23</t>
+  </si>
+  <si>
+    <t>A26</t>
+  </si>
+  <si>
+    <t>4 5 6 8 to 11</t>
   </si>
 </sst>
 </file>
@@ -308,9 +356,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -335,12 +383,17 @@
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FFF0F6FC"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F2328"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -353,8 +406,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="17">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -513,38 +572,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
         <color indexed="64"/>
       </right>
       <top/>
@@ -592,12 +623,222 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
@@ -605,16 +846,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -625,41 +866,228 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="15">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -958,29 +1386,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -992,10 +1420,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -1018,7 +1446,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>301</v>
       </c>
@@ -1041,7 +1469,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>302</v>
       </c>
@@ -1064,7 +1492,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>303</v>
       </c>
@@ -1087,7 +1515,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>304</v>
       </c>
@@ -1110,7 +1538,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>305</v>
       </c>
@@ -1133,7 +1561,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>306</v>
       </c>
@@ -1154,6 +1582,18 @@
       </c>
       <c r="G7" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="24" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="44">
+        <f>COUNTIFS(D2:D7,"Laptop", B2:B7,"North")</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1164,9 +1604,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -1177,7 +1617,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1188,7 +1628,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -1199,7 +1639,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -1217,190 +1657,260 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.54296875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="E1" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="G1" s="28" t="s">
+      <c r="G1" s="31" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="I1" s="27" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="20">
+      <c r="C2" s="15">
         <v>78</v>
       </c>
-      <c r="D2" s="20">
+      <c r="D2" s="15">
         <v>82</v>
       </c>
-      <c r="E2" s="20">
+      <c r="E2" s="15">
         <v>85</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="15">
         <v>92</v>
       </c>
-      <c r="G2" s="29">
+      <c r="G2" s="30">
         <f>AVERAGE(C2:E2)</f>
         <v>81.666666666666671</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2" s="32" t="str">
+        <f>IF(F2&gt;=85,"Eliglible","Not Eligible")</f>
+        <v>Eliglible</v>
+      </c>
+      <c r="I2" t="str">
+        <f>_xlfn.CONCAT(A2,B2)</f>
+        <v>1Rahul</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="20">
+      <c r="C3" s="15">
         <v>88</v>
       </c>
-      <c r="D3" s="20">
+      <c r="D3" s="15">
         <v>91</v>
       </c>
-      <c r="E3" s="20">
+      <c r="E3" s="15">
         <v>90</v>
       </c>
-      <c r="F3" s="20">
+      <c r="F3" s="15">
         <v>96</v>
       </c>
-      <c r="G3" s="29">
+      <c r="G3" s="30">
         <f t="shared" ref="G3:G6" si="0">AVERAGE(C3:E3)</f>
         <v>89.666666666666671</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H3" s="32" t="str">
+        <f t="shared" ref="H3:H6" si="1">IF(F3&gt;=85,"Eliglible","Not Eligible")</f>
+        <v>Eliglible</v>
+      </c>
+      <c r="I3" t="str">
+        <f t="shared" ref="I3:I6" si="2">_xlfn.CONCAT(A3,B3)</f>
+        <v>2Sneha</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="20">
+      <c r="C4" s="15">
         <v>65</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="15">
         <v>70</v>
       </c>
-      <c r="E4" s="20">
+      <c r="E4" s="15">
         <v>72</v>
       </c>
-      <c r="F4" s="20">
+      <c r="F4" s="15">
         <v>85</v>
       </c>
-      <c r="G4" s="29">
+      <c r="G4" s="30">
         <f t="shared" si="0"/>
         <v>69</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H4" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>Eliglible</v>
+      </c>
+      <c r="I4" t="str">
+        <f t="shared" si="2"/>
+        <v>3Arjun</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="15">
         <v>92</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="15">
         <v>89</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="15">
         <v>94</v>
       </c>
-      <c r="F5" s="20">
+      <c r="F5" s="15">
         <v>98</v>
       </c>
-      <c r="G5" s="29">
+      <c r="G5" s="30">
         <f t="shared" si="0"/>
         <v>91.666666666666671</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H5" s="32" t="str">
+        <f t="shared" si="1"/>
+        <v>Eliglible</v>
+      </c>
+      <c r="I5" t="str">
+        <f t="shared" si="2"/>
+        <v>4Pooja</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="22">
         <v>55</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="22">
         <v>60</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="22">
         <v>58</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="22">
         <v>80</v>
       </c>
-      <c r="G6" s="30">
+      <c r="G6" s="33">
         <f t="shared" si="0"/>
         <v>57.666666666666664</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="H6" s="34" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Eligible</v>
+      </c>
+      <c r="I6" t="str">
+        <f t="shared" si="2"/>
+        <v>5Vikas</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" s="24" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="32">
+    <row r="9" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="25">
         <f>MAX(G2:G6)</f>
         <v>91.666666666666671</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="10" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" s="24" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="33"/>
+    <row r="12" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="26">
+        <f>COUNTIF(F2:F6,"&gt;90")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14" s="24" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="35">
+        <f>MEDIAN(C2:E6)</f>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>91</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>42</v>
       </c>
@@ -1408,7 +1918,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>43</v>
       </c>
@@ -1416,7 +1926,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>44</v>
       </c>
@@ -1424,7 +1934,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>45</v>
       </c>
@@ -1432,7 +1942,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>46</v>
       </c>
@@ -1440,7 +1950,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>47</v>
       </c>
@@ -1448,7 +1958,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>48</v>
       </c>
@@ -1456,7 +1966,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>49</v>
       </c>
@@ -1464,7 +1974,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>50</v>
       </c>
@@ -1472,7 +1982,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>51</v>
       </c>
@@ -1480,7 +1990,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>52</v>
       </c>
@@ -1488,7 +1998,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>53</v>
       </c>
@@ -1496,7 +2006,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>54</v>
       </c>
@@ -1504,7 +2014,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>55</v>
       </c>
@@ -1512,7 +2022,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>56</v>
       </c>
@@ -1520,39 +2030,59 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16" s="46" t="s">
         <v>57</v>
       </c>
+      <c r="B16" s="47"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="48"/>
       <c r="J16">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A17" s="49" t="s">
         <v>58</v>
       </c>
+      <c r="B17" s="50"/>
+      <c r="C17" s="50"/>
+      <c r="D17" s="50"/>
+      <c r="E17" s="50"/>
+      <c r="F17" s="51"/>
       <c r="J17">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A18" s="49" t="s">
         <v>59</v>
       </c>
+      <c r="B18" s="50"/>
+      <c r="C18" s="50"/>
+      <c r="D18" s="50"/>
+      <c r="E18" s="50"/>
+      <c r="F18" s="51"/>
       <c r="J18">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    <row r="19" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="52" t="s">
         <v>60</v>
       </c>
+      <c r="B19" s="53"/>
+      <c r="C19" s="53"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="54"/>
       <c r="J19">
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>61</v>
       </c>
@@ -1560,15 +2090,21 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="21" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="55" t="s">
         <v>62</v>
       </c>
+      <c r="B21" s="56"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="57"/>
       <c r="J21">
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>63</v>
       </c>
@@ -1576,15 +2112,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>64</v>
       </c>
+      <c r="H23" t="s">
+        <v>89</v>
+      </c>
       <c r="J23">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>65</v>
       </c>
@@ -1592,7 +2131,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>66</v>
       </c>
@@ -1600,7 +2139,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>67</v>
       </c>
@@ -1608,39 +2147,62 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A27" s="46" t="s">
         <v>68</v>
       </c>
+      <c r="B27" s="47"/>
+      <c r="C27" s="47"/>
+      <c r="D27" s="47"/>
+      <c r="E27" s="47"/>
+      <c r="F27" s="48"/>
+      <c r="I27" t="s">
+        <v>89</v>
+      </c>
       <c r="J27">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A28" s="49" t="s">
         <v>69</v>
       </c>
+      <c r="B28" s="50"/>
+      <c r="C28" s="50"/>
+      <c r="D28" s="50"/>
+      <c r="E28" s="50"/>
+      <c r="F28" s="51"/>
       <c r="J28">
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A29" s="49" t="s">
         <v>70</v>
       </c>
+      <c r="B29" s="50"/>
+      <c r="C29" s="50"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="50"/>
+      <c r="F29" s="51"/>
       <c r="J29">
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+    <row r="30" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="52" t="s">
         <v>71</v>
       </c>
+      <c r="B30" s="53"/>
+      <c r="C30" s="53"/>
+      <c r="D30" s="53"/>
+      <c r="E30" s="53"/>
+      <c r="F30" s="54"/>
       <c r="J30">
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="J32">
         <f>SUM(J1:J30)</f>
         <v>60</v>
@@ -1654,23 +2216,23 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{977BCA3A-0CB3-4E6D-A410-745F4E22A8DA}">
   <dimension ref="A1:L19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.7265625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14" style="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" style="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.28515625" style="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.54296875" style="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.26953125" style="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -1701,14 +2263,14 @@
       <c r="J1" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="L1" s="19" t="s">
+      <c r="L1" s="8" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="11">
         <v>301</v>
       </c>
@@ -1731,7 +2293,7 @@
         <v>14</v>
       </c>
       <c r="H2" s="9">
-        <f>E2*F2</f>
+        <f t="shared" ref="H2:H7" si="0">E2*F2</f>
         <v>90000</v>
       </c>
       <c r="I2" s="9">
@@ -1739,19 +2301,19 @@
         <v>16200</v>
       </c>
       <c r="J2" s="9">
-        <f>H2+I2</f>
+        <f t="shared" ref="J2:J7" si="1">H2+I2</f>
         <v>106200</v>
       </c>
-      <c r="K2" s="4" t="str">
+      <c r="K2" s="15" t="str">
         <f>IF(E2&gt;3,"High","Low")</f>
         <v>Low</v>
       </c>
-      <c r="L2" t="str">
+      <c r="L2" s="4" t="str">
         <f>TEXT(G2,"MMMM")</f>
-        <v>January</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+        <v>May</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="11">
         <v>306</v>
       </c>
@@ -1774,7 +2336,7 @@
         <v>27</v>
       </c>
       <c r="H3" s="9">
-        <f>E3*F3</f>
+        <f t="shared" si="0"/>
         <v>90000</v>
       </c>
       <c r="I3" s="9">
@@ -1782,19 +2344,19 @@
         <v>16200</v>
       </c>
       <c r="J3" s="9">
-        <f>H3+I3</f>
+        <f t="shared" si="1"/>
         <v>106200</v>
       </c>
-      <c r="K3" s="4" t="str">
-        <f t="shared" ref="K3:K7" si="0">IF(E3&gt;3,"High","Low")</f>
+      <c r="K3" s="15" t="str">
+        <f t="shared" ref="K3:K7" si="2">IF(E3&gt;3,"High","Low")</f>
         <v>Low</v>
       </c>
-      <c r="L3" t="str">
-        <f t="shared" ref="L3:L7" si="1">TEXT(G3,"MMMM")</f>
-        <v>January</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L3" s="4" t="str">
+        <f t="shared" ref="L3:L7" si="3">TEXT(G3,"MMMM")</f>
+        <v>18-01-2025</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="11">
         <v>302</v>
       </c>
@@ -1817,7 +2379,7 @@
         <v>18</v>
       </c>
       <c r="H4" s="9">
-        <f>E4*F4</f>
+        <f t="shared" si="0"/>
         <v>75000</v>
       </c>
       <c r="I4" s="9">
@@ -1825,19 +2387,19 @@
         <v>9000</v>
       </c>
       <c r="J4" s="9">
-        <f>H4+I4</f>
+        <f t="shared" si="1"/>
         <v>84000</v>
       </c>
-      <c r="K4" s="4" t="str">
-        <f t="shared" si="0"/>
+      <c r="K4" s="15" t="str">
+        <f t="shared" si="2"/>
         <v>High</v>
       </c>
-      <c r="L4" t="str">
-        <f t="shared" si="1"/>
-        <v>January</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L4" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>July</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="11">
         <v>305</v>
       </c>
@@ -1860,7 +2422,7 @@
         <v>26</v>
       </c>
       <c r="H5" s="9">
-        <f>E5*F5</f>
+        <f t="shared" si="0"/>
         <v>60000</v>
       </c>
       <c r="I5" s="9">
@@ -1868,19 +2430,19 @@
         <v>7200</v>
       </c>
       <c r="J5" s="9">
-        <f>H5+I5</f>
+        <f t="shared" si="1"/>
         <v>67200</v>
       </c>
-      <c r="K5" s="4" t="str">
-        <f t="shared" si="0"/>
+      <c r="K5" s="15" t="str">
+        <f t="shared" si="2"/>
         <v>High</v>
       </c>
-      <c r="L5" t="str">
-        <f t="shared" si="1"/>
-        <v>January</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L5" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>15-01-2025</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="11">
         <v>303</v>
       </c>
@@ -1903,7 +2465,7 @@
         <v>22</v>
       </c>
       <c r="H6" s="9">
-        <f>E6*F6</f>
+        <f t="shared" si="0"/>
         <v>54000</v>
       </c>
       <c r="I6" s="9">
@@ -1911,19 +2473,19 @@
         <v>6480</v>
       </c>
       <c r="J6" s="9">
-        <f>H6+I6</f>
+        <f t="shared" si="1"/>
         <v>60480</v>
       </c>
-      <c r="K6" s="4" t="str">
-        <f t="shared" si="0"/>
+      <c r="K6" s="15" t="str">
+        <f t="shared" si="2"/>
         <v>Low</v>
       </c>
-      <c r="L6" t="str">
-        <f t="shared" si="1"/>
-        <v>January</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L6" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>October</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="11">
         <v>304</v>
       </c>
@@ -1946,7 +2508,7 @@
         <v>25</v>
       </c>
       <c r="H7" s="9">
-        <f>E7*F7</f>
+        <f t="shared" si="0"/>
         <v>45000</v>
       </c>
       <c r="I7" s="9">
@@ -1954,115 +2516,176 @@
         <v>8100</v>
       </c>
       <c r="J7" s="9">
-        <f>H7+I7</f>
+        <f t="shared" si="1"/>
         <v>53100</v>
       </c>
-      <c r="K7" s="4" t="str">
-        <f t="shared" si="0"/>
+      <c r="K7" s="15" t="str">
+        <f t="shared" si="2"/>
         <v>Low</v>
       </c>
-      <c r="L7" t="str">
-        <f t="shared" si="1"/>
-        <v>January</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="17" t="s">
+      <c r="L7" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>December</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="26.5" thickBot="1" x14ac:dyDescent="0.65">
+      <c r="A8" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="21">
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="16">
         <f>SUM(J2:J7)</f>
         <v>477180</v>
       </c>
-      <c r="K8" s="6"/>
-    </row>
-    <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K8" s="22"/>
+      <c r="L8" s="6"/>
+    </row>
+    <row r="9" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="10" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="36">
         <f>COUNTA(E2:E7)</f>
         <v>6</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C10" s="43" t="s">
+        <v>93</v>
+      </c>
+      <c r="E10" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C11" s="42" t="str">
+        <f>LEFT(C2,2)</f>
+        <v>Am</v>
+      </c>
+      <c r="E11" cm="1">
+        <f t="array" ref="E11">COUNTIF(Answer!D2,North)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="B12" s="14"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
+      <c r="B12" s="36"/>
+      <c r="C12" s="40" t="str">
+        <f t="shared" ref="C12:C16" si="4">LEFT(C3,2)</f>
+        <v>Ri</v>
+      </c>
+      <c r="I12" s="45" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A13" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="16">
+      <c r="B13" s="37">
         <f>SUMIF(B2:B7,"North",E2:E7)</f>
         <v>6</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C13" s="40" t="str">
+        <f t="shared" si="4"/>
+        <v>Ri</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="38">
         <f>SUMIF(B2:B7,"South",E2:E7)</f>
         <v>7</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C14" s="40" t="str">
+        <f t="shared" si="4"/>
+        <v>Am</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="38">
         <f>SUMIF(B3:B8,"East",E3:E8)</f>
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C15" s="40" t="str">
+        <f t="shared" si="4"/>
+        <v>Ku</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="39">
         <f>SUMIF(B4:B9,"West",E4:E9)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="22" t="s">
+      <c r="C16" s="41" t="str">
+        <f t="shared" si="4"/>
+        <v>Ne</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="18" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="24">
+    <row r="19" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="19">
         <f>MAX(Answer!J2:J7)</f>
         <v>106200</v>
       </c>
-      <c r="B19" s="25">
+      <c r="B19" s="20">
         <f>MIN(J2:J7)</f>
         <v>53100</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="D1:E8" xr:uid="{977BCA3A-0CB3-4E6D-A410-745F4E22A8DA}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J7">
     <sortCondition descending="1" ref="J2:J7"/>
   </sortState>
   <mergeCells count="1">
     <mergeCell ref="A8:I8"/>
   </mergeCells>
+  <conditionalFormatting sqref="F14">
+    <cfRule type="cellIs" dxfId="8" priority="5" operator="greaterThan">
+      <formula>"&gt;60000"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J7">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="greaterThan">
+      <formula>"&gt;60000"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="greaterThan">
+      <formula>"&gt;60000"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThan">
+      <formula>60000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThan">
+      <formula>"&gt;60000"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>